--- a/KiCAD_Files/FreeDSP_INTEGRA_QUAD-PRO/FreeDSP_INTEGRA_QUAD-PRO-BOMALL.xlsx
+++ b/KiCAD_Files/FreeDSP_INTEGRA_QUAD-PRO/FreeDSP_INTEGRA_QUAD-PRO-BOMALL.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HILO/Documents/KiCad/9.0/projects/FreeDSP_INTEGRA/FreeDSP_INTEGRA_QUAD-PRO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HILO/Documents/KiCad/9.0/projects/KiCAD_Files/FreeDSP_INTEGRA_QUAD-PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC18AA9-F383-F249-8773-179EDAA9F646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81266262-68FA-1141-9B35-C37C9313C260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4820" yWindow="2140" windowWidth="31860" windowHeight="17360" activeTab="1" xr2:uid="{AFBD0D69-82CA-B849-A40F-6BF40B8161E4}"/>
+    <workbookView xWindow="24960" yWindow="9040" windowWidth="31860" windowHeight="19920" activeTab="1" xr2:uid="{AFBD0D69-82CA-B849-A40F-6BF40B8161E4}"/>
   </bookViews>
   <sheets>
     <sheet name="FreeDSP_INTEGRA_QUAD-PRO" sheetId="1" r:id="rId1"/>
-    <sheet name="uP_Logic" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
-    <sheet name="DNP" sheetId="3" r:id="rId4"/>
+    <sheet name="HandMount" sheetId="2" r:id="rId2"/>
+    <sheet name="DNP" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FreeDSP_INTEGRA_QUAD-PRO'!$A$1:$D$1</definedName>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="464">
   <si>
     <t>Footprint</t>
   </si>
@@ -1165,236 +1164,276 @@
     <t>SW7</t>
   </si>
   <si>
+    <t>Myfootprints:RotaryEncoder_TT-Ele_EN11-HSB1AF15</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>PE-65612NL</t>
+  </si>
+  <si>
+    <t>MyLibrary:PE65612NL</t>
+  </si>
+  <si>
+    <t>TP1,TP2,TP3</t>
+  </si>
+  <si>
+    <t>TestPoint_GND,TestPoint_GNDA</t>
+  </si>
+  <si>
+    <t>TestPoint:TestPoint_THTPad_2.0x2.0mm_Drill1.0mm</t>
+  </si>
+  <si>
+    <t>TP4</t>
+  </si>
+  <si>
+    <t>TEST_MP12</t>
+  </si>
+  <si>
+    <t>TestPoint:TestPoint_Pad_D1.0mm</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>GP1UXC41QS</t>
+  </si>
+  <si>
+    <t>U2,U6,U19</t>
+  </si>
+  <si>
+    <t>TPS5430DDAR</t>
+  </si>
+  <si>
+    <t>C9864</t>
+  </si>
+  <si>
+    <t>Package_SO:TI_SO-PowerPAD-8_ThermalVias</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>LM2611AMFX</t>
+  </si>
+  <si>
+    <t>C2072505</t>
+  </si>
+  <si>
+    <t>Package_TO_SOT_SMD:SOT-23-5</t>
+  </si>
+  <si>
+    <t>U4,U5</t>
+  </si>
+  <si>
+    <t>LM317AG-TN3-R</t>
+  </si>
+  <si>
+    <t>C77880</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>PLR135-T10</t>
+  </si>
+  <si>
+    <t>MyLibrary:PLR135-T10</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>74LVC1G86</t>
+  </si>
+  <si>
+    <t>C73458</t>
+  </si>
+  <si>
+    <t>Package_TO_SOT_SMD:SOT-23-5_HandSoldering</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>74LVC1G04</t>
+  </si>
+  <si>
+    <t>C434067</t>
+  </si>
+  <si>
+    <t>digikey-footprints:SOT-753</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>74LVC1G04M5/TR</t>
+  </si>
+  <si>
+    <t>C3007927</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>ADAU1466</t>
+  </si>
+  <si>
+    <t>C654414</t>
+  </si>
+  <si>
+    <t>Myfootprints:LFCSP-72-1EP_10x10mm_P0.5mm_EP5.3x5.3mmL_HandSolder</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>PLT133-T10W</t>
+  </si>
+  <si>
+    <t>MyLibrary:PLT133-T10W</t>
+  </si>
+  <si>
+    <t>U13</t>
+  </si>
+  <si>
+    <t>25AA1024(512)</t>
+  </si>
+  <si>
+    <t>C219767</t>
+  </si>
+  <si>
+    <t>Package_SO:SOIC-8_3.9x4.9mm_P1.27mm</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>XIAO_RP2040</t>
+  </si>
+  <si>
+    <t>Myfootprints:XIAO_RP2040</t>
+  </si>
+  <si>
+    <t>U15,U16</t>
+  </si>
+  <si>
+    <t>OPA1612AIDR</t>
+  </si>
+  <si>
+    <t>C94590</t>
+  </si>
+  <si>
+    <t>U17</t>
+  </si>
+  <si>
+    <t>OSL40391-IX</t>
+  </si>
+  <si>
+    <t>Display_7Segment:LTC-4627Jx</t>
+  </si>
+  <si>
+    <t>U18</t>
+  </si>
+  <si>
+    <t>PIC16F1938-I/SP</t>
+  </si>
+  <si>
+    <t>Package_DIP:DIP-28_W7.62mm</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>OT322524.576MJBA4S</t>
+  </si>
+  <si>
+    <t>C2831388</t>
+  </si>
+  <si>
+    <t>Crystals:Crystal_SMD_TXC_7M-4pin_3.2x2.5mm_HandSoldering</t>
+  </si>
+  <si>
+    <t>Z1</t>
+  </si>
+  <si>
+    <t>LOGO</t>
+  </si>
+  <si>
+    <t>LogoLibrary:SigmaDSP-LogoSmall</t>
+  </si>
+  <si>
+    <t>Z2</t>
+  </si>
+  <si>
+    <t>LogoLibrary:AmaneroLogo</t>
+  </si>
+  <si>
+    <t>Z3</t>
+  </si>
+  <si>
+    <t>LogoLibrary:RasPiLogoSmall</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>LCSC Part #（optional）</t>
+  </si>
+  <si>
+    <t>https://ja.aliexpress.com/item/1005009545686187.html?spm=a2g0o.order_list.order_list_main.5.1f7f585amtVFOu&amp;gatewayAdapt=glo2jpn</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://ja.aliexpress.com/item/1005001485859972.html?spm=a2g0o.order_list.order_list_main.22.6317585agfMs6Y&amp;gatewayAdapt=glo2jpn</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://ja.aliexpress.com/item/1005009571325413.html?spm=a2g0o.productlist.main.2.2c80k3LWk3LWYd&amp;algo_pvid=0a42c07c-60c1-4376-96dc-9d48a74cb99d&amp;algo_exp_id=0a42c07c-60c1-4376-96dc-9d48a74cb99d-1&amp;pdp_ext_f=%7B%22order%22%3A%22-1%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%2115.28%2115.28%21%21%21103.82%21103.82%21%400b1bf20a17776369361035136e5a96%2112000049497951781%21sea%21JP%21230125749%21X%211%210%21n_tag%3A-29919%3Bd%3A8e0556f0%3Bm03_new_user%3A-29895&amp;curPageLogUid=yz0TKIzTcxtk&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005009571325413%7C_p_origin_prod%3A</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://ja.aliexpress.com/item/1005010235537178.html?spm=a2g0o.productlist.main.2.2241puDJpuDJTU&amp;algo_pvid=7364bb38-0635-4dab-b694-ac56c8e501c8&amp;algo_exp_id=7364bb38-0635-4dab-b694-ac56c8e501c8-1&amp;pdp_ext_f=%7B%22order%22%3A%223%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%213.24%213.24%21%21%2122.00%2122.00%21%40212a70c017776372418353604e6d79%2112000051633414164%21sea%21JP%21230125749%21X%211%210%21n_tag%3A-29919%3Bd%3A8e0556f0%3Bm03_new_user%3A-29895&amp;curPageLogUid=5QQvObvGR2vx&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005010235537178%7C_p_origin_prod%3A</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://ja.aliexpress.com/item/1005009992135774.html?spm=a2g0o.detail.pcDetailTopMoreOtherSeller.7.5b67X54LX54L9m&amp;gps-id=pcDetailTopMoreOtherSeller&amp;scm=1007.40050.354490.0&amp;scm_id=1007.40050.354490.0&amp;scm-url=1007.40050.354490.0&amp;pvid=f9e73c94-f9e2-4a38-acee-8151cae56b1b&amp;_t=gps-id%3ApcDetailTopMoreOtherSeller%2Cscm-url%3A1007.40050.354490.0%2Cpvid%3Af9e73c94-f9e2-4a38-acee-8151cae56b1b%2Ctpp_buckets%3A668%232846%238116%232002&amp;pdp_ext_f=%7B%22order%22%3A%2238%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22sceneId%22%3A%2230050%22%2C%22fromPage%22%3A%22recommend%22%7D&amp;pdp_npi=6%40dis%21USD%2143.56%2121.78%21%21%21295.90%21147.95%21%402141115b17776373638078748e38ee%2112000050807766209%21rec%21JP%21230125749%21XZ%211%210%21n_tag%3A-29919%3Bd%3A8e0556f0%3Bm03_new_user%3A-29895&amp;utparam-url=scene%3ApcDetailTopMoreOtherSeller%7Cquery_from%3A%7Cx_object_id%3A1005009992135774%7C_p_origin_prod%3A</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://ja.aliexpress.com/item/1005004552064256.html?spm=a2g0o.productlist.main.10.5928KOlrKOlrUA&amp;algo_pvid=f744d863-2903-455d-92b9-ee42ee86285d&amp;algo_exp_id=f744d863-2903-455d-92b9-ee42ee86285d-9&amp;pdp_ext_f=%7B%22order%22%3A%2240%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%212.19%212.19%21%21%212.19%212.19%21%402151e6dc17776377005814170e4d2e%2112000029581551062%21sea%21JP%21230125749%21X%211%210%21n_tag%3A-29919%3Bd%3A8e0556f0%3Bm03_new_user%3A-29895&amp;curPageLogUid=uJ8MpVJHwzY0&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005004552064256%7C_p_origin_prod%3A</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://ja.aliexpress.com/item/1005008919807552.html?spm=a2g0o.imagesearchproductlist.main.1.3898BXEEBXEEYJ&amp;algo_pvid=6fa8f09f-176d-4672-9422-aab5dff7a50f&amp;algo_exp_id=6fa8f09f-176d-4672-9422-aab5dff7a50f&amp;pdp_ext_f=%7B%22order%22%3A%2218%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%212.65%212.65%21%21%2118.00%2118.00%21%40210156fc17776388483348440e67b4%2112000047206795206%21sea%21JP%21230125749%21X%211%210%21n_tag%3A-29919%3Bd%3A8e0556f0%3Bm03_new_user%3A-29895&amp;curPageLogUid=YvIByTZzOHTp&amp;utparam-url=scene%3Aimage_search%7Cquery_from%3Apc_web_image_search%7Cx_object_id%3A1005008919807552%7C_p_origin_prod%3A</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://ja.aliexpress.com/item/1005008542183827.html?spm=a2g0o.imagesearchproductlist.main.56.43b6SUcuSUcu8r&amp;algo_pvid=8fe93cea-596d-4cfc-8c43-60c4e08d88db&amp;algo_exp_id=8fe93cea-596d-4cfc-8c43-60c4e08d88db&amp;pdp_ext_f=%7B%22order%22%3A%225%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%212.67%211.87%21%21%2118.17%2112.72%21%402101246417776392072625475e9460%2112000045636661875%21sea%21JP%21230125749%21X%211%210%21n_tag%3A-29919%3Bd%3A8e0556f0%3Bm03_new_user%3A-29895&amp;curPageLogUid=pKZ7YVxYECf6&amp;utparam-url=scene%3Aimage_search%7Cquery_from%3Apc_web_image_search%7Cx_object_id%3A1005008542183827%7C_p_origin_prod%3A</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
     <t>EN11-HSB1AF15</t>
-  </si>
-  <si>
-    <t>Myfootprints:RotaryEncoder_TT-Ele_EN11-HSB1AF15</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>PE-65612NL</t>
-  </si>
-  <si>
-    <t>MyLibrary:PE65612NL</t>
-  </si>
-  <si>
-    <t>TP1,TP2,TP3</t>
-  </si>
-  <si>
-    <t>TestPoint_GND,TestPoint_GNDA</t>
-  </si>
-  <si>
-    <t>TestPoint:TestPoint_THTPad_2.0x2.0mm_Drill1.0mm</t>
-  </si>
-  <si>
-    <t>TP4</t>
-  </si>
-  <si>
-    <t>TEST_MP12</t>
-  </si>
-  <si>
-    <t>TestPoint:TestPoint_Pad_D1.0mm</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>GP1UXC41QS</t>
-  </si>
-  <si>
-    <t>U2,U6,U19</t>
-  </si>
-  <si>
-    <t>TPS5430DDAR</t>
-  </si>
-  <si>
-    <t>C9864</t>
-  </si>
-  <si>
-    <t>Package_SO:TI_SO-PowerPAD-8_ThermalVias</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>LM2611AMFX</t>
-  </si>
-  <si>
-    <t>C2072505</t>
-  </si>
-  <si>
-    <t>Package_TO_SOT_SMD:SOT-23-5</t>
-  </si>
-  <si>
-    <t>U4,U5</t>
-  </si>
-  <si>
-    <t>LM317AG-TN3-R</t>
-  </si>
-  <si>
-    <t>C77880</t>
-  </si>
-  <si>
-    <t>U7</t>
-  </si>
-  <si>
-    <t>PLR135-T10</t>
-  </si>
-  <si>
-    <t>MyLibrary:PLR135-T10</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <t>74LVC1G86</t>
-  </si>
-  <si>
-    <t>C73458</t>
-  </si>
-  <si>
-    <t>Package_TO_SOT_SMD:SOT-23-5_HandSoldering</t>
-  </si>
-  <si>
-    <t>U9</t>
-  </si>
-  <si>
-    <t>74LVC1G04</t>
-  </si>
-  <si>
-    <t>C434067</t>
-  </si>
-  <si>
-    <t>digikey-footprints:SOT-753</t>
-  </si>
-  <si>
-    <t>U10</t>
-  </si>
-  <si>
-    <t>74LVC1G04M5/TR</t>
-  </si>
-  <si>
-    <t>C3007927</t>
-  </si>
-  <si>
-    <t>U11</t>
-  </si>
-  <si>
-    <t>ADAU1466</t>
-  </si>
-  <si>
-    <t>C654414</t>
-  </si>
-  <si>
-    <t>Myfootprints:LFCSP-72-1EP_10x10mm_P0.5mm_EP5.3x5.3mmL_HandSolder</t>
-  </si>
-  <si>
-    <t>U12</t>
-  </si>
-  <si>
-    <t>PLT133-T10W</t>
-  </si>
-  <si>
-    <t>MyLibrary:PLT133-T10W</t>
-  </si>
-  <si>
-    <t>U13</t>
-  </si>
-  <si>
-    <t>25AA1024(512)</t>
-  </si>
-  <si>
-    <t>C219767</t>
-  </si>
-  <si>
-    <t>Package_SO:SOIC-8_3.9x4.9mm_P1.27mm</t>
-  </si>
-  <si>
-    <t>U14</t>
-  </si>
-  <si>
-    <t>XIAO_RP2040</t>
-  </si>
-  <si>
-    <t>Myfootprints:XIAO_RP2040</t>
-  </si>
-  <si>
-    <t>U15,U16</t>
-  </si>
-  <si>
-    <t>OPA1612AIDR</t>
-  </si>
-  <si>
-    <t>C94590</t>
-  </si>
-  <si>
-    <t>U17</t>
-  </si>
-  <si>
-    <t>OSL40391-IX</t>
-  </si>
-  <si>
-    <t>Display_7Segment:LTC-4627Jx</t>
-  </si>
-  <si>
-    <t>U18</t>
-  </si>
-  <si>
-    <t>PIC16F1938-I/SP</t>
-  </si>
-  <si>
-    <t>Package_DIP:DIP-28_W7.62mm</t>
-  </si>
-  <si>
-    <t>Y1</t>
-  </si>
-  <si>
-    <t>OT322524.576MJBA4S</t>
-  </si>
-  <si>
-    <t>C2831388</t>
-  </si>
-  <si>
-    <t>Crystals:Crystal_SMD_TXC_7M-4pin_3.2x2.5mm_HandSoldering</t>
-  </si>
-  <si>
-    <t>Z1</t>
-  </si>
-  <si>
-    <t>LOGO</t>
-  </si>
-  <si>
-    <t>LogoLibrary:SigmaDSP-LogoSmall</t>
-  </si>
-  <si>
-    <t>Z2</t>
-  </si>
-  <si>
-    <t>LogoLibrary:AmaneroLogo</t>
-  </si>
-  <si>
-    <t>Z3</t>
-  </si>
-  <si>
-    <t>LogoLibrary:RasPiLogoSmall</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Designator</t>
-  </si>
-  <si>
-    <t>LCSC Part #（optional）</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://ja.aliexpress.com/item/1005005983134515.html?spm=a2g0o.detail.pcDetailTopMoreOtherSeller.4.7bdb639ckKYJmO&amp;gps-id=pcDetailTopMoreOtherSeller&amp;scm=1007.40050.354490.0&amp;scm_id=1007.40050.354490.0&amp;scm-url=1007.40050.354490.0&amp;pvid=c168ece3-2963-42fb-89e7-f5bbdb44fae5&amp;_t=gps-id%3ApcDetailTopMoreOtherSeller%2Cscm-url%3A1007.40050.354490.0%2Cpvid%3Ac168ece3-2963-42fb-89e7-f5bbdb44fae5%2Ctpp_buckets%3A668%232846%238116%232002&amp;pdp_ext_f=%7B%22order%22%3A%225521%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22sceneId%22%3A%2230050%22%2C%22fromPage%22%3A%22recommend%22%7D&amp;pdp_npi=6%40dis%21USD%211.89%211.89%21%21%211.89%211.89%21%402101590d17776394618583376ed074%2112000035172713581%21rec%21JP%21230125749%21XZ%211%210%21n_tag%3A-29919%3Bd%3A8e0556f0%3Bm03_new_user%3A-29895&amp;utparam-url=scene%3ApcDetailTopMoreOtherSeller%7Cquery_from%3A%7Cx_object_id%3A1005005983134515%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>NOP</t>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1560,6 +1599,15 @@
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -1882,7 +1930,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2009,8 +2057,11 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2026,8 +2077,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - アクセント 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -2055,6 +2109,7 @@
     <cellStyle name="タイトル" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="チェック セル" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="どちらでもない" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="ハイパーリンク" xfId="42" builtinId="8"/>
     <cellStyle name="メモ" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="リンク セル" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="悪い" xfId="7" builtinId="27" customBuiltin="1"/>
@@ -2411,30 +2466,30 @@
   <sheetData>
     <row r="1" spans="1:4" s="4" customFormat="1" ht="21">
       <c r="A1" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21">
       <c r="A2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D2" t="s">
         <v>393</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D2" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21">
@@ -2481,16 +2536,16 @@
     </row>
     <row r="6" spans="1:4" ht="21">
       <c r="A6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="21">
@@ -2565,16 +2620,16 @@
     </row>
     <row r="12" spans="1:4" ht="21">
       <c r="A12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C12" t="s">
         <v>251</v>
       </c>
       <c r="D12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="21">
@@ -2607,30 +2662,30 @@
     </row>
     <row r="15" spans="1:4" ht="21">
       <c r="A15" t="s">
+        <v>406</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C15" t="s">
+        <v>408</v>
+      </c>
+      <c r="D15" t="s">
         <v>407</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C15" t="s">
-        <v>409</v>
-      </c>
-      <c r="D15" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="21">
       <c r="A16" t="s">
+        <v>417</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C16" t="s">
+        <v>419</v>
+      </c>
+      <c r="D16" t="s">
         <v>418</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C16" t="s">
-        <v>420</v>
-      </c>
-      <c r="D16" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="21">
@@ -2747,16 +2802,16 @@
     </row>
     <row r="25" spans="1:4" ht="21">
       <c r="A25" t="s">
+        <v>410</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C25" t="s">
+        <v>412</v>
+      </c>
+      <c r="D25" t="s">
         <v>411</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C25" t="s">
-        <v>413</v>
-      </c>
-      <c r="D25" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="21">
@@ -2887,16 +2942,16 @@
     </row>
     <row r="35" spans="1:4" ht="21">
       <c r="A35" t="s">
+        <v>414</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C35" t="s">
+        <v>412</v>
+      </c>
+      <c r="D35" t="s">
         <v>415</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C35" t="s">
-        <v>413</v>
-      </c>
-      <c r="D35" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="21">
@@ -2929,16 +2984,16 @@
     </row>
     <row r="38" spans="1:4" ht="21">
       <c r="A38" t="s">
+        <v>440</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C38" t="s">
+        <v>442</v>
+      </c>
+      <c r="D38" t="s">
         <v>441</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C38" t="s">
-        <v>443</v>
-      </c>
-      <c r="D38" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="42">
@@ -3419,16 +3474,16 @@
     </row>
     <row r="73" spans="1:4" ht="21">
       <c r="A73" t="s">
+        <v>424</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C73" t="s">
+        <v>426</v>
+      </c>
+      <c r="D73" t="s">
         <v>425</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C73" t="s">
-        <v>427</v>
-      </c>
-      <c r="D73" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="21">
@@ -3489,16 +3544,16 @@
     </row>
     <row r="78" spans="1:4" ht="21">
       <c r="A78" t="s">
+        <v>396</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C78" t="s">
+        <v>398</v>
+      </c>
+      <c r="D78" t="s">
         <v>397</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C78" t="s">
-        <v>399</v>
-      </c>
-      <c r="D78" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="21">
@@ -3710,30 +3765,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD4D404-A922-AC49-ACA1-1905227F5849}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="82.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="124.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" ht="21">
+    <row r="1" spans="1:5" s="4" customFormat="1" ht="21">
       <c r="A1" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="21">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="21">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3746,8 +3802,11 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="21">
+      <c r="E2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="21">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -3761,7 +3820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="21">
+    <row r="4" spans="1:5" ht="21">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -3775,7 +3834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="21">
+    <row r="5" spans="1:5" ht="21">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -3789,7 +3848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="21">
+    <row r="6" spans="1:5" ht="21">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -3803,7 +3862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="21">
+    <row r="7" spans="1:5" ht="21">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -3817,7 +3876,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="21">
+    <row r="8" spans="1:5" ht="21">
       <c r="A8" t="s">
         <v>72</v>
       </c>
@@ -3831,7 +3890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="21">
+    <row r="9" spans="1:5" ht="21">
       <c r="A9" t="s">
         <v>134</v>
       </c>
@@ -3845,7 +3904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="21">
+    <row r="10" spans="1:5" ht="21">
       <c r="A10" t="s">
         <v>149</v>
       </c>
@@ -3859,7 +3918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="21">
+    <row r="11" spans="1:5" ht="21">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -3872,8 +3931,11 @@
       <c r="D11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="21">
+      <c r="E11" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="21">
       <c r="A12" t="s">
         <v>155</v>
       </c>
@@ -3886,8 +3948,11 @@
       <c r="D12" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="21">
+      <c r="E12" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21">
       <c r="A13" t="s">
         <v>158</v>
       </c>
@@ -3901,7 +3966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="21">
+    <row r="14" spans="1:5" ht="21">
       <c r="A14" t="s">
         <v>161</v>
       </c>
@@ -3915,7 +3980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="21">
+    <row r="15" spans="1:5" ht="21">
       <c r="A15" t="s">
         <v>164</v>
       </c>
@@ -3929,7 +3994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="21">
+    <row r="16" spans="1:5" ht="21">
       <c r="A16" t="s">
         <v>170</v>
       </c>
@@ -3943,7 +4008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="21">
+    <row r="17" spans="1:5" ht="21">
       <c r="A17" t="s">
         <v>172</v>
       </c>
@@ -3956,8 +4021,11 @@
       <c r="D17" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="21">
+      <c r="E17" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="21">
       <c r="A18" t="s">
         <v>175</v>
       </c>
@@ -3971,7 +4039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="21">
+    <row r="19" spans="1:5" ht="21">
       <c r="A19" t="s">
         <v>158</v>
       </c>
@@ -3985,7 +4053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="21">
+    <row r="20" spans="1:5" ht="21">
       <c r="A20" t="s">
         <v>180</v>
       </c>
@@ -3999,7 +4067,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="21">
+    <row r="21" spans="1:5" ht="21">
       <c r="A21" t="s">
         <v>183</v>
       </c>
@@ -4013,7 +4081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="21">
+    <row r="22" spans="1:5" ht="21">
       <c r="A22" t="s">
         <v>190</v>
       </c>
@@ -4027,7 +4095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="21">
+    <row r="23" spans="1:5" ht="21">
       <c r="A23" t="s">
         <v>240</v>
       </c>
@@ -4041,7 +4109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="21">
+    <row r="24" spans="1:5" ht="21">
       <c r="A24" t="s">
         <v>363</v>
       </c>
@@ -4055,7 +4123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="21">
+    <row r="25" spans="1:5" ht="21">
       <c r="A25" t="s">
         <v>370</v>
       </c>
@@ -4069,7 +4137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="21">
+    <row r="26" spans="1:5" ht="21">
       <c r="A26" t="s">
         <v>373</v>
       </c>
@@ -4082,8 +4150,11 @@
       <c r="D26" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="21">
+      <c r="E26" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21">
       <c r="A27" t="s">
         <v>376</v>
       </c>
@@ -4097,71 +4168,83 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="21">
+    <row r="28" spans="1:5" ht="21">
       <c r="A28" t="s">
-        <v>379</v>
+        <v>461</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>378</v>
       </c>
       <c r="C28" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D28" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="21">
+      <c r="E28" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21">
       <c r="A29" t="s">
+        <v>381</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C29" t="s">
         <v>382</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C29" t="s">
-        <v>383</v>
       </c>
       <c r="D29" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="21">
+      <c r="E29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21">
       <c r="A30" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
+        <v>404</v>
       </c>
       <c r="D30" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="21">
+      <c r="E30" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21">
       <c r="A31" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="C31" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="D31" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="21">
+      <c r="E31" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21">
       <c r="A32" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C32" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="D32" t="s">
         <v>3</v>
@@ -4169,51 +4252,31 @@
     </row>
     <row r="33" spans="1:4" ht="21">
       <c r="A33" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C33" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="21">
-      <c r="A34" t="s">
-        <v>438</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C34" t="s">
-        <v>439</v>
-      </c>
-      <c r="D34" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="18"/>
+  <hyperlinks>
+    <hyperlink ref="E30" r:id="rId1" xr:uid="{CA9B692A-5775-3D43-813E-7CB379DC9AB9}"/>
+    <hyperlink ref="E17" r:id="rId2" xr:uid="{1F76B9CE-0CBA-6740-B978-5A43FB017856}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E13DA42-AEDE-F34F-AE6F-10E6580B5A38}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
-  <sheetData/>
-  <phoneticPr fontId="18"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC3BF9F9-7C3E-A747-9827-318EDEC13BD2}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="34.85546875" bestFit="1" customWidth="1"/>
@@ -4224,16 +4287,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="4" customFormat="1" ht="21">
       <c r="A1" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21">
@@ -4350,13 +4413,13 @@
     </row>
     <row r="10" spans="1:4" ht="21">
       <c r="A10" t="s">
+        <v>384</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C10" t="s">
         <v>385</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C10" t="s">
-        <v>386</v>
       </c>
       <c r="D10" t="s">
         <v>128</v>
@@ -4364,13 +4427,13 @@
     </row>
     <row r="11" spans="1:4" ht="21">
       <c r="A11" t="s">
+        <v>387</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C11" t="s">
         <v>388</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C11" t="s">
-        <v>389</v>
       </c>
       <c r="D11" t="s">
         <v>128</v>
@@ -4378,13 +4441,13 @@
     </row>
     <row r="12" spans="1:4" ht="21">
       <c r="A12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C12" t="s">
         <v>429</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C12" t="s">
-        <v>430</v>
       </c>
       <c r="D12" t="s">
         <v>128</v>
@@ -4392,13 +4455,13 @@
     </row>
     <row r="13" spans="1:4" ht="21">
       <c r="A13" t="s">
+        <v>444</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C13" t="s">
         <v>445</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C13" t="s">
-        <v>446</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -4406,13 +4469,13 @@
     </row>
     <row r="14" spans="1:4" ht="21">
       <c r="A14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C14" t="s">
         <v>447</v>
-      </c>
-      <c r="C14" t="s">
-        <v>448</v>
       </c>
       <c r="D14" t="s">
         <v>128</v>
@@ -4420,13 +4483,13 @@
     </row>
     <row r="15" spans="1:4" ht="21">
       <c r="A15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C15" t="s">
         <v>449</v>
-      </c>
-      <c r="C15" t="s">
-        <v>450</v>
       </c>
       <c r="D15" t="s">
         <v>128</v>
@@ -4556,6 +4619,20 @@
       </c>
       <c r="D24" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="21">
+      <c r="A25" t="s">
+        <v>390</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>
